--- a/A_2018/chrXI:190519-238147_531_finemapping.xlsx
+++ b/A_2018/chrXI:190519-238147_531_finemapping.xlsx
@@ -71176,10 +71176,10 @@
         <v>0.0000000000000000000000591277074923361</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00000000000000000000532149367431025</v>
+        <v>0.00000000000000000000538062138180258</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00000000000000000000466797690728969</v>
+        <v>0.00000000000000000000473021659938689</v>
       </c>
       <c r="J2" t="s">
         <v>726</v>
@@ -71211,10 +71211,10 @@
         <v>0.000109803978965941</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00494117905346737</v>
+        <v>0.00499608104295034</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00433436759076085</v>
+        <v>0.00439215915863766</v>
       </c>
       <c r="J3" t="s">
         <v>732</v>
@@ -71246,10 +71246,10 @@
         <v>0.00077476826168953</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0232430478506859</v>
+        <v>0.0235013039379157</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0203886384655139</v>
+        <v>0.0206604869783875</v>
       </c>
       <c r="J4" t="s">
         <v>738</v>
